--- a/LaneFollowingControlWithSensorFusionAndLaneDetectionExample/tabellarisultati.xlsx
+++ b/LaneFollowingControlWithSensorFusionAndLaneDetectionExample/tabellarisultati.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="15" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="51" uniqueCount="9">
   <si>
     <t>Scenario</t>
   </si>
@@ -37,6 +37,9 @@
   </si>
   <si>
     <t>Fitness_Hecate</t>
+  </si>
+  <si>
+    <t>Panda.m</t>
   </si>
 </sst>
 </file>
@@ -82,7 +85,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.81640625" customWidth="true"/>
@@ -139,10 +142,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C5" s="0">
-        <v>40.206713378310553</v>
+        <v>40.154626672007808</v>
       </c>
     </row>
     <row r="6">
@@ -150,10 +153,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C6" s="0">
-        <v>32.861443385021971</v>
+        <v>32.807297281769891</v>
       </c>
     </row>
     <row r="7">
@@ -161,10 +164,43 @@
         <v>3</v>
       </c>
       <c r="B7" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="0">
+        <v>25.629354485226827</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="0">
-        <v>24.180902039284554</v>
+      <c r="C8" s="0">
+        <v>40.202107995211016</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="0">
+        <v>32.861717388462139</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="0">
+        <v>6.5685656630786724</v>
       </c>
     </row>
   </sheetData>

--- a/LaneFollowingControlWithSensorFusionAndLaneDetectionExample/tabellarisultati.xlsx
+++ b/LaneFollowingControlWithSensorFusionAndLaneDetectionExample/tabellarisultati.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="51" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="78" uniqueCount="10">
   <si>
     <t>Scenario</t>
   </si>
@@ -40,6 +40,9 @@
   </si>
   <si>
     <t>Panda.m</t>
+  </si>
+  <si>
+    <t>A4_Bergamo</t>
   </si>
 </sst>
 </file>
@@ -85,7 +88,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.81640625" customWidth="true"/>
@@ -139,68 +142,101 @@
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C5" s="0">
-        <v>40.154626672007808</v>
+        <v>33.208963129466035</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B6" s="0" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="0">
-        <v>32.807297281769891</v>
+        <v>40.154626672007808</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B7" s="0" t="s">
         <v>8</v>
       </c>
       <c r="C7" s="0">
-        <v>25.629354485226827</v>
+        <v>32.807297281769891</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C8" s="0">
-        <v>40.202107995211016</v>
+        <v>25.629354485226827</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C9" s="0">
-        <v>32.861717388462139</v>
+        <v>33.050151997114838</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="0">
+        <v>40.202107995211016</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="0">
+        <v>32.861717388462139</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="0">
+      <c r="B12" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="0">
         <v>6.5685656630786724</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="0">
+        <v>33.3162792201149</v>
       </c>
     </row>
   </sheetData>

--- a/LaneFollowingControlWithSensorFusionAndLaneDetectionExample/tabellarisultati.xlsx
+++ b/LaneFollowingControlWithSensorFusionAndLaneDetectionExample/tabellarisultati.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="78" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="111" uniqueCount="11">
   <si>
     <t>Scenario</t>
   </si>
@@ -43,6 +43,9 @@
   </si>
   <si>
     <t>A4_Bergamo</t>
+  </si>
+  <si>
+    <t>Anaconda</t>
   </si>
 </sst>
 </file>
@@ -88,7 +91,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.81640625" customWidth="true"/>
@@ -153,90 +156,123 @@
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C6" s="0">
-        <v>40.154626672007808</v>
+        <v>30.94702999784662</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B7" s="0" t="s">
         <v>8</v>
       </c>
       <c r="C7" s="0">
-        <v>32.807297281769891</v>
+        <v>40.154626672007808</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B8" s="0" t="s">
         <v>8</v>
       </c>
       <c r="C8" s="0">
-        <v>25.629354485226827</v>
+        <v>32.807297281769891</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B9" s="0" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="0">
-        <v>33.050151997114838</v>
+        <v>25.629354485226827</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C10" s="0">
-        <v>40.202107995211016</v>
+        <v>33.050151997114838</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C11" s="0">
-        <v>32.861717388462139</v>
+        <v>30.962740151133488</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B12" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C12" s="0">
-        <v>6.5685656630786724</v>
+        <v>40.202107995211016</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="0">
+        <v>32.861717388462139</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="0">
+        <v>6.5685656630786724</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="0">
+      <c r="B15" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="0">
         <v>33.3162792201149</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="0">
+        <v>30.937433890130642</v>
       </c>
     </row>
   </sheetData>

--- a/LaneFollowingControlWithSensorFusionAndLaneDetectionExample/tabellarisultati.xlsx
+++ b/LaneFollowingControlWithSensorFusionAndLaneDetectionExample/tabellarisultati.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="111" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="174" uniqueCount="14">
   <si>
     <t>Scenario</t>
   </si>
@@ -46,6 +46,15 @@
   </si>
   <si>
     <t>Anaconda</t>
+  </si>
+  <si>
+    <t>ACC_01_ISO_TargetDiscriminationTest</t>
+  </si>
+  <si>
+    <t>Colorado.m</t>
+  </si>
+  <si>
+    <t>A4.m</t>
   </si>
 </sst>
 </file>
@@ -91,11 +100,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.81640625" customWidth="true"/>
-    <col min="2" max="2" width="9.6328125" customWidth="true"/>
+    <col min="2" max="2" width="10.7265625" customWidth="true"/>
     <col min="3" max="3" width="13.36328125" customWidth="true"/>
   </cols>
   <sheetData>
@@ -118,7 +127,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="0">
-        <v>40.139505642076038</v>
+        <v>40.145833171463458</v>
       </c>
     </row>
     <row r="3">
@@ -129,7 +138,7 @@
         <v>5</v>
       </c>
       <c r="C3" s="0">
-        <v>32.778807803704908</v>
+        <v>32.809569263513914</v>
       </c>
     </row>
     <row r="4">
@@ -140,7 +149,7 @@
         <v>5</v>
       </c>
       <c r="C4" s="0">
-        <v>24.749103030307012</v>
+        <v>22.017838928658158</v>
       </c>
     </row>
     <row r="5">
@@ -151,7 +160,7 @@
         <v>5</v>
       </c>
       <c r="C5" s="0">
-        <v>33.208963129466035</v>
+        <v>33.229882279081274</v>
       </c>
     </row>
     <row r="6">
@@ -162,117 +171,282 @@
         <v>5</v>
       </c>
       <c r="C6" s="0">
-        <v>30.94702999784662</v>
+        <v>30.755956303763455</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C7" s="0">
-        <v>40.154626672007808</v>
+        <v>49.802777927196701</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B8" s="0" t="s">
         <v>8</v>
       </c>
       <c r="C8" s="0">
-        <v>32.807297281769891</v>
+        <v>40.129656025454075</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B9" s="0" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="0">
-        <v>25.629354485226827</v>
+        <v>32.798168031389402</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B10" s="0" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="0">
-        <v>33.050151997114838</v>
+        <v>26.568991997452919</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" s="0" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="0">
-        <v>30.962740151133488</v>
+        <v>33.203020544767703</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C12" s="0">
-        <v>40.202107995211016</v>
+        <v>30.96665412533568</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C13" s="0">
-        <v>32.861717388462139</v>
+        <v>50.198912485855551</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B14" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C14" s="0">
-        <v>6.5685656630786724</v>
+        <v>40.198763756774866</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B15" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="0">
-        <v>33.3162792201149</v>
+        <v>30.308346551545299</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="0">
+        <v>22.168889762644177</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="0">
+        <v>27.398325126422456</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16" s="0">
-        <v>30.937433890130642</v>
+      <c r="B18" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="0">
+        <v>30.966712812186238</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="0">
+        <v>49.545376555653938</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="B20" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="0">
+        <v>40.162021071193585</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B21" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="0">
+        <v>32.892167691786639</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B22" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" s="0">
+        <v>10.439338970348871</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" s="0">
+        <v>33.195935931757063</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="B24" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" s="0">
+        <v>30.952523680957086</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" s="0">
+        <v>49.822874350175752</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="B26" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" s="0">
+        <v>40.17364891713968</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B27" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="C27" s="0">
+        <v>32.843859309996049</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B28" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="C28" s="0">
+        <v>25.543714011477746</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="0">
+        <v>4.9667712560198929</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="B30" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="C30" s="0">
+        <v>30.975353459770574</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="B31" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" s="0">
+        <v>50.530793849331033</v>
       </c>
     </row>
   </sheetData>

--- a/LaneFollowingControlWithSensorFusionAndLaneDetectionExample/tabellarisultati.xlsx
+++ b/LaneFollowingControlWithSensorFusionAndLaneDetectionExample/tabellarisultati.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="174" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="261" uniqueCount="16">
   <si>
     <t>Scenario</t>
   </si>
@@ -55,6 +55,12 @@
   </si>
   <si>
     <t>A4.m</t>
+  </si>
+  <si>
+    <t>Polo.m</t>
+  </si>
+  <si>
+    <t>Tcross</t>
   </si>
 </sst>
 </file>
@@ -100,7 +106,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.81640625" customWidth="true"/>
@@ -449,6 +455,138 @@
         <v>50.530793849331033</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="B32" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="0">
+        <v>40.170623015461061</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B33" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="C33" s="0">
+        <v>32.856720890620039</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B34" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" s="0">
+        <v>10.979711882153726</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="B35" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" s="0">
+        <v>33.230648809378437</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="B36" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36" s="0">
+        <v>30.957105984381037</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="B37" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="C37" s="0">
+        <v>50.533165806793029</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="B38" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="C38" s="0">
+        <v>40.163328896542708</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B39" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="C39" s="0">
+        <v>2.4033488390879221</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B40" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="C40" s="0">
+        <v>25.634803154595978</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="B41" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="C41" s="0">
+        <v>33.20362214184297</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="B42" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="C42" s="0">
+        <v>30.97983851013975</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="B43" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="C43" s="0">
+        <v>49.938219351809281</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/LaneFollowingControlWithSensorFusionAndLaneDetectionExample/tabellarisultati.xlsx
+++ b/LaneFollowingControlWithSensorFusionAndLaneDetectionExample/tabellarisultati.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="261" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="404" uniqueCount="20">
   <si>
     <t>Scenario</t>
   </si>
@@ -61,6 +61,18 @@
   </si>
   <si>
     <t>Tcross</t>
+  </si>
+  <si>
+    <t>LFACC_01_DoubleCurve_DecelTarget</t>
+  </si>
+  <si>
+    <t>ACC_02_ISO_AutoRetargetTest</t>
+  </si>
+  <si>
+    <t>A7_Milano_Genova</t>
+  </si>
+  <si>
+    <t>FrenataBrusca</t>
   </si>
 </sst>
 </file>
@@ -106,7 +118,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C71"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.81640625" customWidth="true"/>
@@ -193,266 +205,266 @@
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C8" s="0">
-        <v>40.129656025454075</v>
+        <v>29.534781508346462</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C9" s="0">
-        <v>32.798168031389402</v>
+        <v>15.451335109607399</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C10" s="0">
-        <v>26.568991997452919</v>
+        <v>3.73397812150254</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C11" s="0">
-        <v>33.203020544767703</v>
+        <v>28.564850035905799</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B12" s="0" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="0">
-        <v>30.96665412533568</v>
+        <v>40.129656025454075</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="B13" s="0" t="s">
         <v>8</v>
       </c>
       <c r="C13" s="0">
-        <v>50.198912485855551</v>
+        <v>32.798168031389402</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" s="0">
-        <v>40.198763756774866</v>
+        <v>26.568991997452919</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C15" s="0">
-        <v>30.308346551545299</v>
+        <v>33.203020544767703</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C16" s="0">
-        <v>22.168889762644177</v>
+        <v>30.96665412533568</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C17" s="0">
-        <v>27.398325126422456</v>
+        <v>50.198912485855551</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C18" s="0">
-        <v>30.966712812186238</v>
+        <v>29.740558604832692</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C19" s="0">
-        <v>49.545376555653938</v>
+        <v>16.267993007157141</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C20" s="0">
-        <v>40.162021071193585</v>
+        <v>4.2659087417113692</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C21" s="0">
-        <v>32.892167691786639</v>
+        <v>28.710406021508177</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C22" s="0">
-        <v>10.439338970348871</v>
+        <v>40.198763756774866</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C23" s="0">
-        <v>33.195935931757063</v>
+        <v>30.308346551545299</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C24" s="0">
-        <v>30.952523680957086</v>
+        <v>22.168889762644177</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C25" s="0">
-        <v>49.822874350175752</v>
+        <v>27.398325126422456</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C26" s="0">
-        <v>40.17364891713968</v>
+        <v>30.966712812186238</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C27" s="0">
-        <v>32.843859309996049</v>
+        <v>49.545376555653938</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C28" s="0">
-        <v>25.543714011477746</v>
+        <v>29.615205869702237</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C29" s="0">
-        <v>4.9667712560198929</v>
+        <v>17.27836072827979</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C30" s="0">
-        <v>30.975353459770574</v>
+        <v>0.30454350796696161</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C31" s="0">
-        <v>50.530793849331033</v>
+        <v>29.026721012848071</v>
       </c>
     </row>
     <row r="32">
@@ -460,10 +472,10 @@
         <v>1</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C32" s="0">
-        <v>40.170623015461061</v>
+        <v>40.162021071193585</v>
       </c>
     </row>
     <row r="33">
@@ -471,10 +483,10 @@
         <v>2</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C33" s="0">
-        <v>32.856720890620039</v>
+        <v>32.892167691786639</v>
       </c>
     </row>
     <row r="34">
@@ -482,10 +494,10 @@
         <v>3</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C34" s="0">
-        <v>10.979711882153726</v>
+        <v>10.439338970348871</v>
       </c>
     </row>
     <row r="35">
@@ -493,10 +505,10 @@
         <v>9</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C35" s="0">
-        <v>33.230648809378437</v>
+        <v>33.195935931757063</v>
       </c>
     </row>
     <row r="36">
@@ -504,10 +516,10 @@
         <v>10</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C36" s="0">
-        <v>30.957105984381037</v>
+        <v>30.952523680957086</v>
       </c>
     </row>
     <row r="37">
@@ -515,76 +527,384 @@
         <v>11</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C37" s="0">
-        <v>50.533165806793029</v>
+        <v>49.822874350175752</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C38" s="0">
-        <v>40.163328896542708</v>
+        <v>29.242332461396487</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C39" s="0">
-        <v>2.4033488390879221</v>
+        <v>16.851411019931788</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C40" s="0">
-        <v>25.634803154595978</v>
+        <v>-2.5803514835608903</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C41" s="0">
-        <v>33.20362214184297</v>
+        <v>29.177177027689382</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C42" s="0">
-        <v>30.97983851013975</v>
+        <v>40.17364891713968</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B43" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="C43" s="0">
+        <v>32.843859309996049</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B44" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="C44" s="0">
+        <v>25.543714011477746</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="B45" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="C45" s="0">
+        <v>4.9667712560198929</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="B46" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="C46" s="0">
+        <v>30.975353459770574</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="B43" s="0" t="s">
+      <c r="B47" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="C47" s="0">
+        <v>50.530793849331033</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="B48" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="C48" s="0">
+        <v>29.534902640658423</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="B49" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="C49" s="0">
+        <v>16.910167729826547</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="B50" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="C50" s="0">
+        <v>-1.0624538531275665</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="B51" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="C51" s="0">
+        <v>29.033979510562602</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="B52" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="C52" s="0">
+        <v>40.170623015461061</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B53" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="C53" s="0">
+        <v>32.856720890620039</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B54" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="C54" s="0">
+        <v>10.979711882153726</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="B55" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="C55" s="0">
+        <v>33.230648809378437</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="B56" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="C56" s="0">
+        <v>30.957105984381037</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="B57" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="C57" s="0">
+        <v>50.533165806793029</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="B58" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="C58" s="0">
+        <v>29.720336882646521</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="B59" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="C59" s="0">
+        <v>16.835580936498847</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="B60" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="C60" s="0">
+        <v>3.0316564853648114</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="B61" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="C61" s="0">
+        <v>28.988965688207465</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="B62" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="C43" s="0">
+      <c r="C62" s="0">
+        <v>40.163328896542708</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B63" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="C63" s="0">
+        <v>2.4033488390879221</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B64" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="C64" s="0">
+        <v>25.634803154595978</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="B65" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="C65" s="0">
+        <v>33.20362214184297</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="B66" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="C66" s="0">
+        <v>30.97983851013975</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="B67" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="C67" s="0">
         <v>49.938219351809281</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="B68" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="C68" s="0">
+        <v>29.959742399498104</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="B69" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="C69" s="0">
+        <v>16.870495922603986</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="B70" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="C70" s="0">
+        <v>-0.55031151546863377</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="B71" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="C71" s="0">
+        <v>28.979670133966934</v>
       </c>
     </row>
   </sheetData>

--- a/LaneFollowingControlWithSensorFusionAndLaneDetectionExample/tabellarisultati.xlsx
+++ b/LaneFollowingControlWithSensorFusionAndLaneDetectionExample/tabellarisultati.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="404" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="547" uniqueCount="21">
   <si>
     <t>Scenario</t>
   </si>
@@ -73,6 +73,9 @@
   </si>
   <si>
     <t>FrenataBrusca</t>
+  </si>
+  <si>
+    <t>Highway_double_target</t>
   </si>
 </sst>
 </file>
@@ -227,13 +230,13 @@
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B10" s="0" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="0">
-        <v>3.73397812150254</v>
+        <v>39.82686101201962</v>
       </c>
     </row>
     <row r="11">
@@ -337,13 +340,13 @@
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B20" s="0" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="0">
-        <v>4.2659087417113692</v>
+        <v>43.568877088224845</v>
       </c>
     </row>
     <row r="21">
@@ -447,13 +450,13 @@
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B30" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C30" s="0">
-        <v>0.30454350796696161</v>
+        <v>43.668292538098775</v>
       </c>
     </row>
     <row r="31">
@@ -557,13 +560,13 @@
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B40" s="0" t="s">
         <v>12</v>
       </c>
       <c r="C40" s="0">
-        <v>-2.5803514835608903</v>
+        <v>43.037552396657858</v>
       </c>
     </row>
     <row r="41">
@@ -667,13 +670,13 @@
     </row>
     <row r="50">
       <c r="A50" s="0" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B50" s="0" t="s">
         <v>13</v>
       </c>
       <c r="C50" s="0">
-        <v>-1.0624538531275665</v>
+        <v>44.878457488199906</v>
       </c>
     </row>
     <row r="51">
@@ -777,13 +780,13 @@
     </row>
     <row r="60">
       <c r="A60" s="0" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B60" s="0" t="s">
         <v>14</v>
       </c>
       <c r="C60" s="0">
-        <v>3.0316564853648114</v>
+        <v>45.267474773366743</v>
       </c>
     </row>
     <row r="61">
@@ -887,13 +890,13 @@
     </row>
     <row r="70">
       <c r="A70" s="0" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B70" s="0" t="s">
         <v>15</v>
       </c>
       <c r="C70" s="0">
-        <v>-0.55031151546863377</v>
+        <v>43.77004414281123</v>
       </c>
     </row>
     <row r="71">
